--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73A0A80-1E66-4590-8EB6-BEF8EFCF5965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543E8572-FA15-49B9-95C5-26985445A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12660" yWindow="-14820" windowWidth="14535" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="135" yWindow="-14205" windowWidth="14625" windowHeight="13725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -440,7 +449,8 @@
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>0</v>
+        <f>A2+16000</f>
+        <v>16000</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543E8572-FA15-49B9-95C5-26985445A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025D78A1-B83C-42E7-923D-C9CF30627C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="-14205" windowWidth="14625" windowHeight="13725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="-13515" windowWidth="9675" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
+    <sheet name="reference" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -59,6 +60,58 @@
     <t>通常攻撃</t>
     <rPh sb="0" eb="4">
       <t>ツウジョウコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>select</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正面1マス</t>
+    <rPh sb="0" eb="2">
+      <t>ショウメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行動者</t>
+    <rPh sb="0" eb="3">
+      <t>コウドウシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP1回復</t>
+    <rPh sb="3" eb="5">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP20回復</t>
+    <rPh sb="4" eb="6">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満腹度100回復</t>
+    <rPh sb="0" eb="3">
+      <t>マンプクド</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満腹度30HP20回復</t>
+    <rPh sb="0" eb="3">
+      <t>マンプクド</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイフク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -83,7 +136,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -93,6 +146,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -124,10 +183,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -408,17 +468,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +493,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -443,8 +504,11 @@
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -455,20 +519,188 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
+        <f>VLOOKUP(E2,reference!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="F2" s="2">
-        <v>-1</v>
-      </c>
       <c r="G2" s="2">
         <v>-1</v>
       </c>
       <c r="H2" s="2">
         <v>-1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2">
+        <v>100</v>
+      </c>
+      <c r="B3" s="2">
+        <f t="shared" ref="B3:B6" si="0">A3+16000</f>
+        <v>16100</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3">
+        <f>VLOOKUP(E3,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2">
+        <v>101</v>
+      </c>
+      <c r="B4" s="2">
+        <f t="shared" si="0"/>
+        <v>16101</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3">
+        <f>VLOOKUP(E4,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2">
+        <v>102</v>
+      </c>
+      <c r="B5" s="2">
+        <f t="shared" si="0"/>
+        <v>16102</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3">
+        <f>VLOOKUP(E5,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2">
+        <v>103</v>
+      </c>
+      <c r="B6" s="2">
+        <f t="shared" si="0"/>
+        <v>16103</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3">
+        <f>VLOOKUP(E6,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4922D76A-161D-4910-BD59-38C8E567B196}">
+          <x14:formula1>
+            <xm:f>reference!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E6</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61363DC4-4EF8-4A17-979D-A53F7AB69E25}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025D78A1-B83C-42E7-923D-C9CF30627C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0D50B4-1465-4C3F-A7C8-F41143C13551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="-13515" windowWidth="9675" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="930" yWindow="-14610" windowWidth="16995" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -112,6 +112,23 @@
     </rPh>
     <rPh sb="9" eb="11">
       <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>焼き攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腐らせる</t>
+    <rPh sb="0" eb="1">
+      <t>クサ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -468,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -541,27 +558,27 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2">
-        <f t="shared" ref="B3:B6" si="0">A3+16000</f>
-        <v>16100</v>
+        <f t="shared" ref="B3:B4" si="0">A3+16000</f>
+        <v>16001</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3">
         <f>VLOOKUP(E3,reference!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H3" s="2">
         <v>-1</v>
@@ -572,24 +589,24 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
         <f t="shared" si="0"/>
-        <v>16101</v>
+        <v>16002</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3">
         <f>VLOOKUP(E4,reference!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G4" s="2">
         <v>-1</v>
@@ -603,14 +620,14 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B5" s="2">
-        <f t="shared" si="0"/>
-        <v>16102</v>
+        <f t="shared" ref="B5:B8" si="1">A5+16000</f>
+        <v>16100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3">
         <f>VLOOKUP(E5,reference!A:B,2,FALSE)</f>
@@ -620,10 +637,10 @@
         <v>8</v>
       </c>
       <c r="F5" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="H5" s="2">
         <v>-1</v>
@@ -634,14 +651,14 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B6" s="2">
-        <f t="shared" si="0"/>
-        <v>16103</v>
+        <f t="shared" si="1"/>
+        <v>16101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3">
         <f>VLOOKUP(E6,reference!A:B,2,FALSE)</f>
@@ -651,15 +668,77 @@
         <v>8</v>
       </c>
       <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2">
+        <v>102</v>
+      </c>
+      <c r="B7" s="2">
+        <f t="shared" si="1"/>
+        <v>16102</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3">
+        <f>VLOOKUP(E7,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2">
+        <v>103</v>
+      </c>
+      <c r="B8" s="2">
+        <f t="shared" si="1"/>
+        <v>16103</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3">
+        <f>VLOOKUP(E8,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="2">
         <v>4</v>
       </c>
-      <c r="G6" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H6" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="G8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -674,7 +753,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E6</xm:sqref>
+          <xm:sqref>E2:E8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0D50B4-1465-4C3F-A7C8-F41143C13551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59132AB6-DA6B-4A5D-A2D2-0F5A549978F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="-14610" windowWidth="16995" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -129,6 +129,20 @@
     <t>腐らせる</t>
     <rPh sb="0" eb="1">
       <t>クサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正面10マス</t>
+    <rPh sb="0" eb="2">
+      <t>ショウメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>場所替え</t>
+    <rPh sb="0" eb="3">
+      <t>バショガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -485,13 +499,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="9" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
@@ -739,6 +753,37 @@
         <v>-1</v>
       </c>
       <c r="I8" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2">
+        <v>104</v>
+      </c>
+      <c r="B9" s="2">
+        <f t="shared" ref="B9" si="2">A9+16000</f>
+        <v>16104</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3">
+        <f>VLOOKUP(E9,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8</v>
+      </c>
+      <c r="G9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -753,7 +798,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E8</xm:sqref>
+          <xm:sqref>E2:E9</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -763,8 +808,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61363DC4-4EF8-4A17-979D-A53F7AB69E25}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -782,8 +830,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59132AB6-DA6B-4A5D-A2D2-0F5A549978F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645878CB-3B9C-4C04-B513-A231BD7432DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20160" yWindow="-4035" windowWidth="19095" windowHeight="15030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
